--- a/RELATORIOS/duplicados_para_validar.xlsx
+++ b/RELATORIOS/duplicados_para_validar.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L124"/>
+  <dimension ref="A1:L183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="14" customWidth="1" style="5" min="2" max="2"/>
@@ -824,7 +824,6 @@
           <t>COD ID_219298069 (linha 541).jpg</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2004 Av. João Paulo II</t>
@@ -835,8 +834,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9" ht="15.75" customHeight="1" s="5">
       <c r="B9" t="inlineStr">
@@ -869,7 +866,6 @@
           <t>COD ID_219298069 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>1115 Av. João Paulo II</t>
@@ -880,8 +876,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10" ht="15.75" customHeight="1" s="5">
       <c r="B10" t="inlineStr">
@@ -914,7 +908,6 @@
           <t>COD ID_219298070 (linha 529).jpg</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>56 R. Geralda Detoni</t>
@@ -925,8 +918,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11" ht="15.75" customHeight="1" s="5">
       <c r="B11" t="inlineStr">
@@ -959,7 +950,6 @@
           <t>COD ID_219298070 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>56 R. Geralda Detoni</t>
@@ -970,8 +960,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12" ht="15.75" customHeight="1" s="5">
       <c r="B12" t="inlineStr">
@@ -1004,7 +992,6 @@
           <t>COD ID_219298164 (linha 691).jpg</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>136 R. José Natal</t>
@@ -1052,11 +1039,6 @@
           <t>COD ID_219298164 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="5">
       <c r="B14" t="inlineStr">
@@ -1089,7 +1071,6 @@
           <t>COD ID_219298165 (linha 689).jpg</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>84 R. José Natal</t>
@@ -1137,11 +1118,6 @@
           <t>COD ID_219298165 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="5">
       <c r="B16" t="inlineStr">
@@ -1174,7 +1150,6 @@
           <t>COD ID_219298197 (linha 700).jpg</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>500 R. Paul Harris</t>
@@ -1185,8 +1160,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="5">
       <c r="B17" t="inlineStr">
@@ -1214,11 +1187,6 @@
           <t>COD ID_219298197 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18" ht="15.75" customHeight="1" s="5">
       <c r="B18" t="inlineStr">
@@ -1251,7 +1219,6 @@
           <t>COD ID_219298203 (linha 581).jpg</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>305 Tv. Dez</t>
@@ -1262,8 +1229,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" s="5">
       <c r="B19" t="inlineStr">
@@ -1291,11 +1256,6 @@
           <t>COD ID_219298203 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20" ht="15.75" customHeight="1" s="5">
       <c r="B20" t="inlineStr">
@@ -1328,7 +1288,6 @@
           <t>COD ID_219298208 (linha 311).jpg</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>19 R. Ipiao</t>
@@ -1339,8 +1298,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="5">
       <c r="B21" t="inlineStr">
@@ -1373,7 +1330,6 @@
           <t>COD ID_219298208 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>19 R. Ipiao</t>
@@ -1384,8 +1340,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="5">
       <c r="B22" t="inlineStr">
@@ -1418,7 +1372,6 @@
           <t>COD ID_219298349 (linha 321).jpg</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>418 R. Cap. José Porfírio</t>
@@ -1429,8 +1382,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="5">
       <c r="B23" t="inlineStr">
@@ -1463,7 +1414,6 @@
           <t>COD ID_219298349 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>418 R. Cap. José Porfírio</t>
@@ -1474,8 +1424,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -1508,7 +1456,6 @@
           <t>COD ID_219991165 (linha 903).jpg</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>85 R. Carmen de Oliveira Lara</t>
@@ -1519,8 +1466,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
@@ -1553,7 +1498,6 @@
           <t>COD ID_219991165 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>110 R. Carmen de Oliveira Lara</t>
@@ -1564,8 +1508,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
@@ -1598,7 +1540,6 @@
           <t>COD ID_219991188 (linha 351).jpg</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>58 R. do Garimpo</t>
@@ -1651,7 +1592,6 @@
           <t>COD ID_219991188 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>540 R. Cassiano Lemos</t>
@@ -1662,8 +1602,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -1696,7 +1634,6 @@
           <t>COD ID_219991759 (linha 238).jpg</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>362 R. Cap. José Porfírio</t>
@@ -1749,7 +1686,6 @@
           <t>COD ID_219991759 (linha 322).jpg</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>381 R. Cap. José Porfírio</t>
@@ -1802,7 +1738,6 @@
           <t>COD ID_219991759 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>2 R. Dr. Baracuí</t>
@@ -1813,8 +1748,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
@@ -1847,7 +1780,6 @@
           <t>COD ID_219991945 (linha 461).jpg</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>1 R. Funcionário João Rosa</t>
@@ -1900,7 +1832,6 @@
           <t>COD ID_219991945 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>1 R. Funcionário João Rosa</t>
@@ -1953,7 +1884,6 @@
           <t>COD ID_219991956 (linha 317).jpg</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>612 R. Cap. José Porfírio</t>
@@ -1964,8 +1894,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
@@ -1998,7 +1926,6 @@
           <t>COD ID_219991956 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>585 R. Cap. José Porfírio</t>
@@ -2009,8 +1936,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
@@ -2043,7 +1968,6 @@
           <t>COD ID_219991957 (linha 313).jpg</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>26 R. Ipiao</t>
@@ -2054,8 +1978,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
@@ -2088,7 +2010,6 @@
           <t>COD ID_219991957 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>26 R. Ipiao</t>
@@ -2099,8 +2020,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
@@ -2133,7 +2052,6 @@
           <t>COD ID_219992424 (linha 846).jpg</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>1941 R. Santo Antônio</t>
@@ -2144,8 +2062,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="B38" t="inlineStr">
@@ -2178,7 +2094,6 @@
           <t>COD ID_219992424 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>2 R. Dorvalina Pereira de Melo</t>
@@ -2231,7 +2146,6 @@
           <t>COD ID_220780172 (linha 505).jpg</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>120 R. José Primo de Melo</t>
@@ -2284,7 +2198,6 @@
           <t>COD ID_220780172 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>151 R. José Primo de Melo</t>
@@ -2337,7 +2250,6 @@
           <t>COD ID_220780173 (linha 509).jpg</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>105 R. Funcionário João Rosa</t>
@@ -2348,8 +2260,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
@@ -2382,7 +2292,6 @@
           <t>COD ID_220780173 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>94 R. Funcionário João Rosa</t>
@@ -2393,8 +2302,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
@@ -2427,7 +2334,6 @@
           <t>COD ID_220780179 (linha 315).jpg</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>675 R. Cap. José Porfírio</t>
@@ -2438,8 +2344,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
@@ -2472,7 +2376,6 @@
           <t>COD ID_220780179 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>675 R. Cap. José Porfírio</t>
@@ -2483,8 +2386,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
@@ -2517,7 +2418,6 @@
           <t>COD ID_220780180 (linha 314).jpg</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>79 R. Ipiao</t>
@@ -2528,8 +2428,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
@@ -2562,7 +2460,6 @@
           <t>COD ID_220780180 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>77 R. Ipiao</t>
@@ -2573,8 +2470,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" t="inlineStr">
@@ -2607,7 +2502,6 @@
           <t>COD ID_220780258 (linha 407).jpg</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>121 R. Carvalho Lopes</t>
@@ -2618,8 +2512,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" t="inlineStr">
@@ -2652,7 +2544,6 @@
           <t>COD ID_220780258 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>131 R. Carvalho Lopes</t>
@@ -2663,8 +2554,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
@@ -2697,7 +2586,6 @@
           <t>COD ID_220853333 (linha 479).jpg</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>55 R. Padre Antônio Marcigaglia</t>
@@ -2708,8 +2596,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" t="inlineStr">
@@ -2742,7 +2628,6 @@
           <t>COD ID_220853333 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>65 R. Maria J Borges</t>
@@ -2753,8 +2638,6 @@
           <t>NAO</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
@@ -2787,7 +2670,6 @@
           <t>COD ID_220853350 (linha 323).jpg</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>331 R. Cap. José Porfírio</t>
@@ -2798,8 +2680,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" t="inlineStr">
@@ -2832,7 +2712,6 @@
           <t>COD ID_220853350 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>349 R. Cap. José Porfírio</t>
@@ -2843,8 +2722,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" t="inlineStr">
@@ -2877,7 +2754,6 @@
           <t>COD ID_221621656 (linha 553).jpg</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>71 R. Elói Teixeira</t>
@@ -2888,8 +2764,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" t="inlineStr">
@@ -2922,7 +2796,6 @@
           <t>COD ID_221621656 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>164 R. Geralda Detoni</t>
@@ -2975,7 +2848,6 @@
           <t>COD ID_221621687 (linha 259).jpg</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>46 Av. João Paulo II</t>
@@ -2986,8 +2858,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
@@ -3020,7 +2890,6 @@
           <t>COD ID_221621687 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>46 Av. João Paulo II</t>
@@ -3031,8 +2900,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" t="inlineStr">
@@ -3065,7 +2932,6 @@
           <t>COD ID_221621699 (linha 316).jpg</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>650 R. Cap. José Porfírio</t>
@@ -3076,8 +2942,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" t="inlineStr">
@@ -3110,7 +2974,6 @@
           <t>COD ID_221621699 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>625 R. Cap. José Porfírio</t>
@@ -3121,8 +2984,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" t="inlineStr">
@@ -3155,7 +3016,6 @@
           <t>COD ID_221621705 (linha 360).jpg</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>138 R. Consolação</t>
@@ -3208,7 +3068,6 @@
           <t>COD ID_221621705 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>138 R. Consolação</t>
@@ -3261,7 +3120,6 @@
           <t>COD ID_221621789 (linha 406).jpg</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>160 R. Carvalho Lopes</t>
@@ -3272,8 +3130,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" t="inlineStr">
@@ -3306,7 +3162,6 @@
           <t>COD ID_221621789 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>131 R. Carvalho Lopes</t>
@@ -3317,8 +3172,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" t="inlineStr">
@@ -3351,7 +3204,6 @@
           <t>COD ID_221621797 (linha 324).jpg</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>323 R. Cap. José Porfírio</t>
@@ -3362,8 +3214,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" t="inlineStr">
@@ -3396,7 +3246,6 @@
           <t>COD ID_221621797 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>323 R. Cap. José Porfírio</t>
@@ -3407,8 +3256,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" t="inlineStr">
@@ -3441,7 +3288,6 @@
           <t>COD ID_221705430 (linha 886).jpg</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>98 R. José Pereira Valle</t>
@@ -3452,8 +3298,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" t="inlineStr">
@@ -3486,7 +3330,6 @@
           <t>COD ID_221705430 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>125 R. José Pereira Valle</t>
@@ -3497,8 +3340,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="B67" t="inlineStr">
@@ -3531,7 +3372,6 @@
           <t>COD ID_222494508 (linha 328).jpg</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>118 R. Joaquim Antônio Dutra</t>
@@ -3542,8 +3382,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="B68" t="inlineStr">
@@ -3576,7 +3414,6 @@
           <t>COD ID_222494508 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>118 R. Joaquim Antônio Dutra</t>
@@ -3587,8 +3424,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="B69" t="inlineStr">
@@ -3621,7 +3456,6 @@
           <t>COD ID_222494603 (linha 476).jpg</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>138 R. Padre Leão</t>
@@ -3632,8 +3466,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" t="inlineStr">
@@ -3666,7 +3498,6 @@
           <t>COD ID_222494603 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>21 R. Maria J Borges</t>
@@ -3677,8 +3508,6 @@
           <t>NAO</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" t="inlineStr">
@@ -3711,7 +3540,6 @@
           <t>COD ID_222495590 (linha 860).jpg</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>15 R. Jovino Augusto da Silva</t>
@@ -3764,7 +3592,6 @@
           <t>COD ID_222495590 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>15 R. Jovino Augusto da Silva</t>
@@ -3817,7 +3644,6 @@
           <t>COD ID_222571821 (linha 790).jpg</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>165 R. José Veloso de Paiva</t>
@@ -3828,8 +3654,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="B74" t="inlineStr">
@@ -3862,7 +3686,6 @@
           <t>COD ID_222571821 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>40 R. Helvecio Tadeu Vaz</t>
@@ -3915,7 +3738,6 @@
           <t>COD ID_223390192 (linha 432).jpg</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2 R. Laurindo Baleeiro</t>
@@ -3968,7 +3790,6 @@
           <t>COD ID_223390192 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>480 MG-428</t>
@@ -3979,8 +3800,6 @@
           <t>NAO</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" t="inlineStr">
@@ -4013,7 +3832,6 @@
           <t>COD ID_223390385 (linha 320).jpg</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>510 R. Cap. José Porfírio</t>
@@ -4024,8 +3842,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" t="inlineStr">
@@ -4058,7 +3874,6 @@
           <t>COD ID_223390385 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>510 R. Cap. José Porfírio</t>
@@ -4069,8 +3884,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" t="inlineStr">
@@ -4103,7 +3916,6 @@
           <t>COD ID_223390425 (linha 606).jpg</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>778 R. Perdizes</t>
@@ -4156,7 +3968,6 @@
           <t>COD ID_223390425 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>778 R. Perdizes</t>
@@ -4209,7 +4020,6 @@
           <t>COD ID_223390442 (linha 326).jpg</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>52 R. Joaquim Antônio Dutra</t>
@@ -4220,8 +4030,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" t="inlineStr">
@@ -4254,7 +4062,6 @@
           <t>COD ID_223390442 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>52 R. Joaquim Antônio Dutra</t>
@@ -4265,8 +4072,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" t="inlineStr">
@@ -4299,7 +4104,6 @@
           <t>COD ID_223456906 (linha 878).jpg</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>240 R. José Pereira Valle</t>
@@ -4310,8 +4114,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" t="inlineStr">
@@ -4344,7 +4146,6 @@
           <t>COD ID_223456906 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>10 R. Hércules Afonso de Oliveira</t>
@@ -4355,8 +4156,6 @@
           <t>NAO</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" t="inlineStr">
@@ -4389,7 +4188,6 @@
           <t>COD ID_223694251 (linha 820).jpg</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>90 R. Ana Paula Balduino</t>
@@ -4400,8 +4198,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" t="inlineStr">
@@ -4434,7 +4230,6 @@
           <t>COD ID_223694251 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>120 R. Ana Paula Balduino</t>
@@ -4445,8 +4240,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" t="inlineStr">
@@ -4479,7 +4272,6 @@
           <t>COD ID_223751195 (linha 402).jpg</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>211 R. Carvalho Lopes</t>
@@ -4490,8 +4282,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" t="inlineStr">
@@ -4524,7 +4314,6 @@
           <t>COD ID_223751195 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>211 R. Carvalho Lopes</t>
@@ -4535,8 +4324,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="B89" t="inlineStr">
@@ -4569,7 +4356,6 @@
           <t>COD ID_223977029 (linha 682).jpg</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>84 R. Carlos Barbosa</t>
@@ -4622,7 +4408,6 @@
           <t>COD ID_223977029 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>244 R. Padre Antônio Marcigaglia</t>
@@ -4633,8 +4418,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="B91" t="inlineStr">
@@ -4667,7 +4450,6 @@
           <t>COD ID_223977056 (linha 327).jpg</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>90 R. Joaquim Antônio Dutra</t>
@@ -4678,8 +4460,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="B92" t="inlineStr">
@@ -4712,7 +4492,6 @@
           <t>COD ID_223977056 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>81 R. Joaquim Antônio Dutra</t>
@@ -4723,8 +4502,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="B93" t="inlineStr">
@@ -4757,7 +4534,6 @@
           <t>COD ID_223979101 (linha 876).jpg</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>290 R. José Pereira Valle</t>
@@ -4768,8 +4544,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="B94" t="inlineStr">
@@ -4802,7 +4576,6 @@
           <t>COD ID_223979101 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>35 R. Hércules Afonso de Oliveira</t>
@@ -4855,7 +4628,6 @@
           <t>COD ID_224318089 (linha 318).jpg</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>570 R. Cap. José Porfírio</t>
@@ -4866,8 +4638,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="B96" t="inlineStr">
@@ -4900,7 +4670,6 @@
           <t>COD ID_224318089 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>555 R. Cap. José Porfírio</t>
@@ -4911,8 +4680,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="B97" t="inlineStr">
@@ -4945,7 +4712,6 @@
           <t>COD ID_224318090 (linha 319).jpg</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>546 R. Cap. José Porfírio</t>
@@ -4956,8 +4722,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="B98" t="inlineStr">
@@ -4990,7 +4754,6 @@
           <t>COD ID_224318090 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>546 R. Cap. José Porfírio</t>
@@ -5001,8 +4764,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="B99" t="inlineStr">
@@ -5035,7 +4796,6 @@
           <t>COD ID_224318094 (linha 312).jpg</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>720 R. Cap. José Porfírio</t>
@@ -5046,8 +4806,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="B100" t="inlineStr">
@@ -5080,7 +4838,6 @@
           <t>COD ID_224318094 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>720 R. Cap. José Porfírio</t>
@@ -5091,8 +4848,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="B101" t="inlineStr">
@@ -5125,7 +4880,6 @@
           <t>COD ID_224318367 (linha 473).jpg</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>99 R. Padre Leão</t>
@@ -5136,8 +4890,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="B102" t="inlineStr">
@@ -5170,7 +4922,6 @@
           <t>COD ID_224318367 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>91 R. Padre Leão</t>
@@ -5181,8 +4932,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="B103" t="inlineStr">
@@ -5215,7 +4964,6 @@
           <t>COD ID_224357564 (linha 52).jpg</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>1205 R. José Carlos Pedro Grande</t>
@@ -5268,7 +5016,6 @@
           <t>COD ID_224357564 (linha 742).jpg</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>145 R. Benedita Margarida da Mota</t>
@@ -5279,8 +5026,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="B105" t="inlineStr">
@@ -5313,7 +5058,6 @@
           <t>COD ID_224357628 (linha 863).jpg</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>85 R. Jovino Augusto da Silva</t>
@@ -5324,8 +5068,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="B106" t="inlineStr">
@@ -5358,7 +5100,6 @@
           <t>COD ID_224357628 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>80 R. Jovino Augusto da Silva</t>
@@ -5369,8 +5110,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="B107" t="inlineStr">
@@ -5403,7 +5142,6 @@
           <t>COD ID_224357653 (linha 845).jpg</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>1963 R. Santo Antônio</t>
@@ -5414,8 +5152,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="B108" t="inlineStr">
@@ -5448,7 +5184,6 @@
           <t>COD ID_224357653 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>2 R. Dorvalina Pereira de Melo</t>
@@ -5501,7 +5236,6 @@
           <t>COD ID_224359052 (linha 884).jpg</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>140 R. José Pereira Valle</t>
@@ -5512,8 +5246,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="B110" t="inlineStr">
@@ -5546,7 +5278,6 @@
           <t>COD ID_224359052 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>140 R. José Pereira Valle</t>
@@ -5557,8 +5288,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="B111" t="inlineStr">
@@ -5591,7 +5320,6 @@
           <t>COD ID_224495808 (linha 798).jpg</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>360 R. Domingos Leandro Silva</t>
@@ -5644,7 +5372,6 @@
           <t>COD ID_224495808 (linha 800).jpg</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>Araxá, State of Minas Gerais</t>
@@ -5655,8 +5382,6 @@
           <t>(sem dado de rua)</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="B113" t="inlineStr">
@@ -5689,7 +5414,6 @@
           <t>COD ID_224495808 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>410 R. Domingos Leandro Silva</t>
@@ -5742,7 +5466,6 @@
           <t>COD ID_350236506 (linha 262).jpg</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>779 R. Cap. José Porfírio</t>
@@ -5795,7 +5518,6 @@
           <t>COD ID_350236506 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>130 Av. João Paulo II</t>
@@ -5806,8 +5528,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="B116" t="inlineStr">
@@ -5840,7 +5560,6 @@
           <t>COD ID_350236509 (linha 291).jpg</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>371 R. Mal. Deodoro</t>
@@ -5851,8 +5570,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="B117" t="inlineStr">
@@ -5885,7 +5602,6 @@
           <t>COD ID_350236509 (linha 292).jpg</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>616 R. Ipiao</t>
@@ -5933,11 +5649,6 @@
           <t>COD ID_350236509 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="B119" t="inlineStr">
@@ -5970,7 +5681,6 @@
           <t>COD ID_350236584 (linha 325).jpg</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>30 R. Joaquim Antônio Dutra</t>
@@ -5981,8 +5691,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="B120" t="inlineStr">
@@ -6010,11 +5718,6 @@
           <t>COD ID_350236584 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="B121" t="inlineStr">
@@ -6047,7 +5750,6 @@
           <t>COD ID_922742634 (linha 522).jpg</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>203 R. Laurindo Baleeiro</t>
@@ -6058,8 +5760,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="B122" t="inlineStr">
@@ -6087,11 +5787,6 @@
           <t>COD ID_922742634 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="B123" t="inlineStr">
@@ -6124,7 +5819,6 @@
           <t>COD ID_922742665 (linha 517).jpg</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>448 R. Santa Juliana</t>
@@ -6135,8 +5829,6 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="B124" t="inlineStr">
@@ -6169,7 +5861,6 @@
           <t>COD ID_922742665 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>448 R. Santa Juliana</t>
@@ -6180,8 +5871,2084 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1834912248</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6124423906,-46.9437033846</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>COD ID_1834912248 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1834912248</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>974</v>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.612401,-46.9434153,3a,75y,315.58h,109.82t/data=!3m7!1e1!3m5!1sgS3yxt9Pya48kl7mZPnJOg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-19.818728571042413%26panoid%3DgS3yxt9Pya48kl7mZPnJOg%26yaw%3D315.5795100182921!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AVENIDA GERALDO PORFIRIO BOTELHO 2088, 2088, FERTIZA</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6124423906,-46.9437033846</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>COD ID_1834912248 (linha 974).jpg</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2057 Av. Geraldo Porfírio Botelho</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>220853354</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6118937754,-46.9426482226</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>COD ID_220853354 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>220853354</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>990</v>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6116421,-46.9423169,3a,90y,220.91h,117.65t/data=!3m7!1e1!3m5!1sZajLlsNdP1OR01TzrTtF7g!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-27.65385159472983%26panoid%3DZajLlsNdP1OR01TzrTtF7g%26yaw%3D220.91226250555349!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AVENIDA GERALDO PORFIRIO BOTELHO 2040, 2040, FERTIZA</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6118937754,-46.9426482226</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>COD ID_220853354 (linha 990).jpg</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>131 R. José da Cruz</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>219991762 (dist=51.5m)</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>RUA SANTA CRUZ 307, 307, FERTIZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>222494485</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6107537057,-46.9453321692</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>COD ID_222494485 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>222494485</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>1016</v>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6099714,-46.9455412,3a,75y,92.36h,116.51t/data=!3m7!1e1!3m5!1sORwDb3L41lGD_0oJpHjNdA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-26.50904547366504%26panoid%3DORwDb3L41lGD_0oJpHjNdA%26yaw%3D92.36477269466307!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>RUA ANTONIO BARRETO 490, 490, FERTIZA</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6107537057,-46.9453321692</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>COD ID_222494485 (linha 1016).jpg</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>319 R. Benedito Rezende</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>221705458 (dist=33.3m)</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>RUA BENEDITO REZENDE 319, 319, FERTIZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>221705458</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6096759024,-46.9455955933</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>COD ID_221705458 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>221705458</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.609786,-46.9455543,3a,90y,14.63h,101.89t/data=!3m7!1e1!3m5!1sYcrwmKBIUluEvO5xM5w6uw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-11.891881408826961%26panoid%3DYcrwmKBIUluEvO5xM5w6uw%26yaw%3D14.629895405955097!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>RUA BENEDITO REZENDE 319, 319, FERTIZA</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6096759024,-46.9455955933</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>COD ID_221705458 (linha 1020).jpg</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>319 R. Benedito Rezende</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>220855406</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6099295886,-46.9455319905</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>COD ID_220855406 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>220855406</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6100583,-46.9454949,3a,48.9y,5.22h,104t/data=!3m7!1e1!3m5!1sN233kfjKSzrOuQM4dVx1xA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-13.999470230600565%26panoid%3DN233kfjKSzrOuQM4dVx1xA%26yaw%3D5.221688051899513!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>RUA SELDA DE CASTRO ALVES 486, 486, FERTIZA</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6099295886,-46.9455319905</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>COD ID_220855406 (linha 1021).jpg</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2 R. Benedito Rezende</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>223979113 (dist=23.4m)</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>RUA BENEDITO REZENDE 495, 495, FERTIZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>219386131</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6099418931,-46.9452270727</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>COD ID_219386131 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>219386131</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>1023</v>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6099829,-46.9452027,3a,75y,15.05h,113.89t/data=!3m7!1e1!3m5!1sUUkdFGx0SfGbb6ivKwiXSA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-23.88582694326236%26panoid%3DUUkdFGx0SfGbb6ivKwiXSA%26yaw%3D15.049103542453434!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>RUA SELDA DE CASTRO ALVES 466, 466, FERTIZA</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6099418931,-46.9452270727</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>COD ID_219386131 (linha 1023).jpg</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>475 R. Selda de Castro Alves</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>222496777</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6100526,-46.9446186,3a,90y,96.14h,108.76t/data=!3m7!1e1!3m5!1srXPA6a5j8JPsZkW70c9VdA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-18.762060245754824%26panoid%3DrXPA6a5j8JPsZkW70c9VdA%26yaw%3D96.13567271217379!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>RUA ARGENTINA DE OLIVEIRA FERREIRA 437, 437, FERTIZA</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6100660526,-46.9445994781</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>COD ID_222496777 (linha 1026).jpg</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>437 R. Argentina de Oliveira Ferreira</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>222496777</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>1036</v>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6101483,-46.9445944,3a,48.9y,28.13h,107.42t/data=!3m7!1e1!3m5!1sNeC4BkOkMVOPKTqedUDKkQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-17.422826029732704%26panoid%3DNeC4BkOkMVOPKTqedUDKkQ%26yaw%3D28.13264598506657!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>RUA ARGENTINA DE OLIVEIRA FERREIRA 437, 437, FERTIZA</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6100660526,-46.9445994781</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>COD ID_222496777 (linha 1036).jpg</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>460 R. Argentina de Oliveira Ferreira</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>219991187</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>1027</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6103298,-46.9445487,3a,75y,104.36h,118.19t/data=!3m7!1e1!3m5!1saw1wVBY2aFrscvIktGOC2w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-28.189011681042288%26panoid%3Daw1wVBY2aFrscvIktGOC2w%26yaw%3D104.36436345011532!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>RUA ARGENTINA DE OLIVEIRA FERREIRA 467, 467, FERTIZA</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6103015779,-46.9445451096</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>COD ID_219991187 (linha 1027).jpg</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>470 R. Argentina de Oliveira Ferreira</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>219991187</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>1037</v>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6103298,-46.9445487,3a,75y,93.2h,112.85t/data=!3m7!1e1!3m5!1saw1wVBY2aFrscvIktGOC2w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-22.85192325861452%26panoid%3Daw1wVBY2aFrscvIktGOC2w%26yaw%3D93.19822630519084!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>RUA ARGENTINA DE OLIVEIRA FERREIRA 467, 467, FERTIZA</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6103015779,-46.9445451096</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>COD ID_219991187 (linha 1037).jpg</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>470 R. Argentina de Oliveira Ferreira</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>224318083</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6105733368,-46.9444720792</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>COD ID_224318083 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>224318083</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1038</v>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6106122,-46.9444884,3a,75y,61.95h,112.54t/data=!3m7!1e1!3m5!1sAD0JjkGV6hypMgSQxH0Okg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-22.537997300812137%26panoid%3DAD0JjkGV6hypMgSQxH0Okg%26yaw%3D61.951609443501226!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>RUA ARGENTINA DE OLIVEIRA FERREIRA 497, 497, FERTIZA</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6105733368,-46.9444720792</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>COD ID_224318083 (linha 1038).jpg</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>498 R. Argentina de Oliveira Ferreira</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>221986532</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.592390367,-46.9377152065</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>COD ID_221986532 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>221986532</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>1131</v>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5924507,-46.9377133,3a,73.9y,237.89h,124.07t/data=!3m7!1e1!3m5!1so9Ko-ce7ZL06V26Fbx34eQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-34.07006710843076%26panoid%3Do9Ko-ce7ZL06V26Fbx34eQ%26yaw%3D237.88740201547705!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>RUA MARIANO DE AVILA 116, 116, CENTRO</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.592390367,-46.9377152065</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>COD ID_221986532 (linha 1131).jpg</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>130 R. Mariano de Ávila</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>221704223</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5920530304,-46.9396841147</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>COD ID_221704223 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>221704223</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>1170</v>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5920379,-46.9397249,3a,90y,79.5h,132.78t/data=!3m7!1e1!3m5!1s89oDY0udMsj1U-I7RJWXlg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-42.77638677545053%26panoid%3D89oDY0udMsj1U-I7RJWXlg%26yaw%3D79.49649750944641!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>RUA DOM JOSE GASPAR 62, 62, CENTRO</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5920530304,-46.9396841147</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>COD ID_221704223 (linha 1170).jpg</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>41 R. Dom José Gáspar</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>220854040</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5930832623,-46.9362747129</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>COD ID_220854040 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>220854040</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>1208</v>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5930852,-46.9362085,3a,90y,312.03h,125.38t/data=!3m7!1e1!3m5!1sLOtF00utT_6IegzckBCStQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-35.37535652183968%26panoid%3DLOtF00utT_6IegzckBCStQ%26yaw%3D312.03109335362944!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>RUA ALMEIDA CAMPOS 84, 84, CENTRO</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5930832623,-46.9362747129</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>COD ID_220854040 (linha 1208).jpg</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>84 R. Almeida Campos</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>223455903</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>1217</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5932975,-46.9352157,3a,90y,106.04h,130t/data=!3m7!1e1!3m5!1sUo0vGeUk0_S-OhhmukMJBQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-39.995778301895115%26panoid%3DUo0vGeUk0_S-OhhmukMJBQ%26yaw%3D106.0437671196359!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>RUA NOSSA SENHORA DA CONCEICAO 25, 25, CENTRO</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5933296981,-46.9352006832</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>COD ID_223455903 (linha 1217).jpg</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>20 R. Nossa Sra. da Conceição</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>223455903</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>1226</v>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5932975,-46.9352157,3a,90y,95.6h,133.73t/data=!3m7!1e1!3m5!1sUo0vGeUk0_S-OhhmukMJBQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-43.734133258226564%26panoid%3DUo0vGeUk0_S-OhhmukMJBQ%26yaw%3D95.60357107231692!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>RUA NOSSA SENHORA DA CONCEICAO 25, 25, CENTRO</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5933296981,-46.9352006832</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>COD ID_223455903 (linha 1226).jpg</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>20 R. Nossa Sra. da Conceição</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>350236609</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5855253769,-46.9383289057</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>COD ID_350236609 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>350236609</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>1283</v>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5855402,-46.9382906,3a,75y,100.58h,116.97t/data=!3m7!1e1!3m5!1sfKA02kmX74jdudvyR6IItA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-26.972438510795925%26panoid%3DfKA02kmX74jdudvyR6IItA%26yaw%3D100.57534015753876!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>RUA TEOFILO DOS SANTOS 268, 268, RICA</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5855253769,-46.9383289057</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>COD ID_350236609 (linha 1283).jpg</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>268 R. Teófilo dos Santos</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>350236609</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>1284</v>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5854746,-46.938394,3a,45.3y,79.69h,104.22t/data=!3m7!1e1!3m5!1s47wjzFLY28WYcdy4AlbiiA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-14.216830485973105%26panoid%3D47wjzFLY28WYcdy4AlbiiA%26yaw%3D79.69311782842526!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>RUA TEOFILO DOS SANTOS 268, 268, RICA</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5855253769,-46.9383289057</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>COD ID_350236609 (linha 1284).jpg</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>274 R. Teófilo dos Santos</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>219385325</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5885936,-46.9347644,3a,90y,21.69h,115.45t/data=!3m7!1e1!3m5!1sIfeDYxA2p9lXvMOejnyQ7g!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-25.449002195587653%26panoid%3DIfeDYxA2p9lXvMOejnyQ7g%26yaw%3D21.692641453590706!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>RUA ITACURU 551, 551, CENTRO</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5885553736,-46.9348100186</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>COD ID_219385325 (linha 1114).jpg</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>454 R. Alexandre Gondin</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>223455767 (dist=38.0m)</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>RUA ALEXANDRE GONDIM 305, 305, CENTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>219385325</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>1298</v>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5885936,-46.9347644,3a,90y,10.6h,112.34t/data=!3m7!1e1!3m5!1sIfeDYxA2p9lXvMOejnyQ7g!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-22.339512163266022%26panoid%3DIfeDYxA2p9lXvMOejnyQ7g%26yaw%3D10.596300429163449!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>RUA ITACURU 551, 551, CENTRO</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5885553736,-46.9348100186</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>COD ID_219385325 (linha 1298).jpg</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>454 R. Alexandre Gondin</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>223455767 (dist=38.0m)</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>RUA ALEXANDRE GONDIM 305, 305, CENTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>221528351</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.588568082,-46.9378314637</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>COD ID_221528351 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>221528351</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>1316</v>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5886327,-46.9378296,3a,31.3y,226.3h,107.49t/data=!3m7!1e1!3m5!1sSj9r7JawO4H7AeSHP3xgEQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-17.492388914795896%26panoid%3DSj9r7JawO4H7AeSHP3xgEQ%26yaw%3D226.2998717885746!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>RUA PADRE ANCHIETA 155, 155, CENTRO</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.588568082,-46.9378314637</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>COD ID_221528351 (linha 1316).jpg</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>114 R. Padre Anchieta</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>219384986</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5860750057,-46.9386688971</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>COD ID_219384986 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>219384986</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>1334</v>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5860495,-46.9386805,3a,41.2y,222.54h,111.7t/data=!3m7!1e1!3m5!1sN8UWd3RMNFhcMCzqyWuK0Q!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-21.697495715559896%26panoid%3DN8UWd3RMNFhcMCzqyWuK0Q%26yaw%3D222.53639796594425!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>RUA ABDANUR ELIAS 67, 67, RICA</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5860750057,-46.9386688971</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>COD ID_219384986 (linha 1334).jpg</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>186 R. Abdanur Elías</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>223977792</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.584664,-46.9388839,3a,41.1y,172.56h,114.88t/data=!3m7!1e1!3m5!1siAdt8fgM30Au7JBgsg_j4Q!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-24.881706546993485%26panoid%3DiAdt8fgM30Au7JBgsg_j4Q%26yaw%3D172.55531262987918!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>RUA JOAO VERCOSA 220, 220, SAO PEDRO</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5847532226,-46.9389390183</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>COD ID_223977792 (linha 190).jpg</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>207 R. João Verçosa</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>223977792</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>1336</v>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.584664,-46.9388839,3a,64.6y,165.51h,112.33t/data=!3m7!1e1!3m5!1siAdt8fgM30Au7JBgsg_j4Q!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-22.333443832332833%26panoid%3DiAdt8fgM30Au7JBgsg_j4Q%26yaw%3D165.51250916737123!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>RUA JOAO VERCOSA 220, 220, SAO PEDRO</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5847532226,-46.9389390183</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>COD ID_223977792 (linha 1336).jpg</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>207 R. João Verçosa</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>222494803</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>1279</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5849405,-46.938999,3a,80.1y,169.75h,123.8t/data=!3m7!1e1!3m5!1sP523mmhYzopo6vFt5jl1TQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-33.800910555194264%26panoid%3DP523mmhYzopo6vFt5jl1TQ%26yaw%3D169.74557993953565!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>RUA TEOFILO DOS SANTOS 337, 337, SAO PEDRO</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5849871156,-46.9390371865</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>COD ID_222494803 (linha 1279).jpg</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>192 R. João Verçosa</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>350236679 (dist=11.7m)</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>RUA JOAO VERCOSA 169, 169, SAO PEDRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>222494803</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>1337</v>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5849405,-46.938999,3a,75y,160.9h,114.88t/data=!3m7!1e1!3m5!1sP523mmhYzopo6vFt5jl1TQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-24.880764827369163%26panoid%3DP523mmhYzopo6vFt5jl1TQ%26yaw%3D160.9015148382235!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>RUA TEOFILO DOS SANTOS 337, 337, SAO PEDRO</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5849871156,-46.9390371865</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>COD ID_222494803 (linha 1337).jpg</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>192 R. João Verçosa</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>350236679 (dist=11.7m)</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>RUA JOAO VERCOSA 169, 169, SAO PEDRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>223390411</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5853931855,-46.94326418</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>COD ID_223390411 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>223390411</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>1364</v>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5853808,-46.9433261,3a,39.1y,193.64h,101.2t/data=!3m7!1e1!3m5!1sJanB-w9FYP22DT9gp2GrjA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-11.199667958457098%26panoid%3DJanB-w9FYP22DT9gp2GrjA%26yaw%3D193.63639648538563!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>RUA IMBIACA 737, 737, CENTRO</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5853931855,-46.94326418</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>COD ID_223390411 (linha 1364).jpg</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>47 R. Imbiaca</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>350236672</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5859295241,-46.9412024383</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>COD ID_350236672 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>350236672</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>1365</v>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5859752,-46.9411725,3a,90y,308.14h,121.08t/data=!3m7!1e1!3m5!1snmAvs8uu_HP1PWYp3iQFuQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-31.078026445110993%26panoid%3DnmAvs8uu_HP1PWYp3iQFuQ%26yaw%3D308.1449144627438!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>RUA BENTO ANTONIO 149, 149, CENTRO</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5859295241,-46.9412024383</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>COD ID_350236672 (linha 1365).jpg</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>157 R. Bento Antônio</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>219991729</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5861053407,-46.9425674042</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>COD ID_219991729 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>219991729</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>1370</v>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5861206,-46.942462,3a,75y,310.9h,103.41t/data=!3m7!1e1!3m5!1sOP9NhEYp7dpWZ-2bpTl4UA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-13.414937033887824%26panoid%3DOP9NhEYp7dpWZ-2bpTl4UA%26yaw%3D310.8997444210115!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>RUA MARIO CAMPOS 557, 557, CENTRO</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5861053407,-46.9425674042</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>COD ID_219991729 (linha 1370).jpg</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>550 R. Mario Campos</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>224357759</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5894299059,-46.9391665981</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>COD ID_224357759 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>224357759</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>1388</v>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5894488,-46.9390412,3a,61.5y,271.77h,103t/data=!3m7!1e1!3m5!1sBtidRXJQ73OrUkpUe30zEQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-12.999600234504427%26panoid%3DBtidRXJQ73OrUkpUe30zEQ%26yaw%3D271.77198363561655!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AVENIDA VEREADOR JOAO SENA 83, 83, CENTRO</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5894299059,-46.9391665981</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>COD ID_224357759 (linha 1388).jpg</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>93 Av. Ver. João Sena</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>223977847</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5892576075,-46.9392312126</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>COD ID_223977847 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>223977847</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>1390</v>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5892573,-46.9392534,3a,90y,72.04h,114.57t/data=!3m7!1e1!3m5!1sjAI3Um3rtYQctL4PDb_U9w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-24.56875887393339%26panoid%3DjAI3Um3rtYQctL4PDb_U9w%26yaw%3D72.04359260770099!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AVENIDA VEREADOR JOAO SENA 52, 52, CENTRO</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5892576075,-46.9392312126</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>COD ID_223977847 (linha 1390).jpg</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>123 Av. Ver. João Sena</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>223976919</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.588175509,-46.9407337369</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>COD ID_223976919 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>223976919</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>1399</v>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5883059,-46.9408761,3a,75y,259.48h,105.07t/data=!3m7!1e1!3m5!1sndMgJiLPvldI4S89MWTeQw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-15.069729073462113%26panoid%3DndMgJiLPvldI4S89MWTeQw%26yaw%3D259.48265437366246!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AVENIDA VEREADOR JOAO SENA 296, 296, CENTRO</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.588175509,-46.9407337369</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>COD ID_223976919 (linha 1399).jpg</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>31 Praça São Sebastião</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>223977033</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5860168,-46.9436505,3a,90y,351.93h,116.53t/data=!3m7!1e1!3m5!1shY5zXK4Es8R2gQ-0FTSNlg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-26.534484811002002%26panoid%3DhY5zXK4Es8R2gQ-0FTSNlg%26yaw%3D351.9310052722952!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AVENIDA VEREADOR JOAO SENA 738, 738, CENTRO</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5859760991,-46.9436618656</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>COD ID_223977033 (linha 1413).jpg</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>732 Av. Ver. João Sena</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>223977033</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>1426</v>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5860168,-46.9436505,3a,75y,249.01h,103.59t/data=!3m7!1e1!3m5!1shY5zXK4Es8R2gQ-0FTSNlg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-13.589358108002415%26panoid%3DhY5zXK4Es8R2gQ-0FTSNlg%26yaw%3D249.00803289657384!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AVENIDA VEREADOR JOAO SENA 738, 738, CENTRO</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5859760991,-46.9436618656</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>COD ID_223977033 (linha 1426).jpg</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>732 Av. Ver. João Sena</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>224318350</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>1412</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.586199,-46.9434182,3a,90y,338.74h,110.66t/data=!3m7!1e1!3m5!1sindNZA6hblF6NjgW94xxqw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-20.66164492273664%26panoid%3DindNZA6hblF6NjgW94xxqw%26yaw%3D338.74227401548285!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>AVENIDA VEREADOR JOAO SENA 0, 0, CENTRO</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5861317745,-46.9434635831</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>COD ID_224318350 (linha 1412).jpg</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>587 Av. Ver. João Sena</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>224318350</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>1427</v>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.586199,-46.9434182,3a,90y,206.28h,111.32t/data=!3m7!1e1!3m5!1sindNZA6hblF6NjgW94xxqw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-21.322073905552557%26panoid%3DindNZA6hblF6NjgW94xxqw%26yaw%3D206.28344773881108!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AVENIDA VEREADOR JOAO SENA 0, 0, CENTRO</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5861317745,-46.9434635831</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>COD ID_224318350 (linha 1427).jpg</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>587 Av. Ver. João Sena</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>223976996</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5870907054,-46.9424934601</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>COD ID_223976996 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>223976996</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>1431</v>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5870585,-46.9423608,3a,90y,268.61h,108.51t/data=!3m7!1e1!3m5!1sGN4hBOEArH0sF1uWP8ZyTQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-18.509662177126742%26panoid%3DGN4hBOEArH0sF1uWP8ZyTQ%26yaw%3D268.6149196836148!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>AVENIDA VEREADOR JOAO SENA 445, 445, CENTRO</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5870907054,-46.9424934601</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>COD ID_223976996 (linha 1431).jpg</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>445 Av. Ver. João Sena</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>223976929</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5878769521,-46.9416165393</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>COD ID_223976929 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>223976929</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>1438</v>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5878526,-46.9415375,3a,90y,263.8h,125.99t/data=!3m7!1e1!3m5!1sNLVmmTxzE6ZWJhEFWzI6tg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-35.988990345762716%26panoid%3DNLVmmTxzE6ZWJhEFWzI6tg%26yaw%3D263.7990065191903!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>RUA DOUTOR BARACUHY 9, 9, CENTRO</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5878769521,-46.9416165393</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>COD ID_223976929 (linha 1438).jpg</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>18 R. Dr. Baracuí</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="B1:H23">
@@ -6429,6 +8196,103 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId237"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId238"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F128" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F136" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F147" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F148" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F166" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId336"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RELATORIOS/duplicados_para_validar.xlsx
+++ b/RELATORIOS/duplicados_para_validar.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L183"/>
+  <dimension ref="A1:L193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="14" customWidth="1" style="5" min="2" max="2"/>
@@ -7889,8 +7889,6 @@
           <t>lote anterior</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
       <c r="F182" s="2" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5878769521,-46.9416165393</t>
@@ -7901,11 +7899,6 @@
           <t>COD ID_223976929 (linha lote anterior).jpg</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="B183" t="inlineStr">
@@ -7936,7 +7929,6 @@
           <t>COD ID_223976929 (linha 1438).jpg</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
           <t>18 R. Dr. Baracuí</t>
@@ -7947,8 +7939,326 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>219298324</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5987290082,-46.9421470134</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>COD ID_219298324 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>219298324</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>1490</v>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5986096,-46.9421769,3a,46.9y,158.5h,109.11t/data=!3m7!1e1!3m5!1sDpGZcIQO-H0L2aNLa_RsYw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-19.109686132592287%26panoid%3DDpGZcIQO-H0L2aNLa_RsYw%26yaw%3D158.49849176112087!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1615, 1615, SAO CRISTOVAO</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5987290082,-46.9421470134</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>COD ID_219298324 (linha 1490).jpg</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>1510 Av. Pref. Aracely de Paula</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>219991693</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5980368306,-46.9418337004</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>COD ID_219991693 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>219991693</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>1492</v>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5981139,-46.9418988,3a,41.2y,45.34h,110.48t/data=!3m7!1e1!3m5!1suS_OPDWEM1LTaJ1fxTEpeA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-20.48031833548788%26panoid%3DuS_OPDWEM1LTaJ1fxTEpeA%26yaw%3D45.33803043467011!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1530, 1530, CENTRO</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5980368306,-46.9418337004</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>COD ID_219991693 (linha 1492).jpg</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>349 Av. Pref. Aracely de Paula</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>223455631</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.595395806,-46.9396288649</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>COD ID_223455631 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>223455631</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>1534</v>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5954696,-46.9395495,3a,75y,329.7h,116.82t/data=!3m7!1e1!3m5!1sDN-cQqsRE8vbMO7W7H0IYg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-26.819060972950837%26panoid%3DDN-cQqsRE8vbMO7W7H0IYg%26yaw%3D329.7040524850523!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>RUA DOM BOSCO 153, 153, CENTRO</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.595395806,-46.9396288649</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>COD ID_223455631 (linha 1534).jpg</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>60 R. Dom Bôsco</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>219991697</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6013904466,-46.9407777614</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>COD ID_219991697 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>219991697</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>1641</v>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6014152,-46.9407331,3a,90y,333.52h,132.46t/data=!3m7!1e1!3m5!1sMOZU-ZlZvfNYQQsc2W7S1w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-42.45931187128633%26panoid%3DMOZU-ZlZvfNYQQsc2W7S1w%26yaw%3D333.5209523458089!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>RUA JOAO BATISTA FERNANDES 55, 55, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6013904466,-46.9407777614</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>COD ID_219991697 (linha 1641).jpg</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>15 R. João Batista Fernandes</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>223390371</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6014218743,-46.9412166548</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>COD ID_223390371 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>223390371</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>1642</v>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6014512,-46.9412085,3a,90y,2.49h,139.08t/data=!3m7!1e1!3m5!1sulznL7OFwcq1XqAPr3DupQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-49.07767963929405%26panoid%3DulznL7OFwcq1XqAPr3DupQ%26yaw%3D2.4899684284229693!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>RUA JOAO BATISTA FERNANDES 100, 100, JOAO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6014218743,-46.9412166548</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>COD ID_223390371 (linha 1642).jpg</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>75 R. João Batista Fernandes</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="B1:H23">
@@ -8293,6 +8603,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId334"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId335"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F190" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F191" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F192" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F193" r:id="rId351"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RELATORIOS/duplicados_para_validar.xlsx
+++ b/RELATORIOS/duplicados_para_validar.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M160"/>
+  <dimension ref="A1:M250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7222,6 +7222,3894 @@
           <t>SIM</t>
         </is>
       </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>220854179</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6021889403,-46.9337243165</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>COD ID_220854179 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>220854179</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>1786</v>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6022379,-46.933833,3a,34.3y,66.62h,103.44t/data=!3m7!1e1!3m5!1sN6rCX7bGXuqUN8MpXKvY-g!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-13.4407645345957%26panoid%3DN6rCX7bGXuqUN8MpXKvY-g%26yaw%3D66.61703828420525!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyNC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>RUA GIL RODRIGUES 160, 160, SAO VICENTE</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6021889403,-46.9337243165</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>COD ID_220854179 (linha 1786).jpg</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>230 R. Gil Rodrigues</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>224223465</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5924832166,-46.9383167675</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>COD ID_224223465 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>224223465</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>1176</v>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5924339,-46.9382782,3a,63.6y,280.01h,122.09t/data=!3m7!1e1!3m5!1sCIHM0ogKEICAgICkoqHZKw!2e10!6shttps:%2F%2Flh3.googleusercontent.com%2Fgpms-cs-s%2FAFP8RcOGr98TNtNAP15Sirnwt5BxhZRdjntT-J0vSyHdnfv_rq1B8M2KfwXj6beWWYTitPHj8I5dEY6EEQfz64_Pf5bOi--YHMtOvuN0ZNLUen3JhWu2PceHsE3vQ8MDjE3laCXM7ZY%3Dw900-h600-k-no-pi-32.090209432138224-ya280.00917728977015-ro0-fo100!7i5376!8i2688?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>RUA PRESIDENTE OLEGARIO MACIEL 194, 194, CENTRO</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5924832166,-46.9383167675</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>COD ID_224223465 (linha 1176).jpg</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>(sem dado de rua)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>220857400</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6067836117,-46.9289655206</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>COD ID_220857400 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>220857400</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>1867</v>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6067299,-46.9288907,3a,43y,222.02h,104.08t/data=!3m7!1e1!3m5!1s0e6YdhnALFoJ4od7-HEiVA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-14.075132207355296%26panoid%3D0e6YdhnALFoJ4od7-HEiVA%26yaw%3D222.02116180488164!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>RUA DIVINO ALVES FERREIRA 225, 225, SANTO ANTONIO</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6067836117,-46.9289655206</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>COD ID_220857400 (linha 1867).jpg</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>1 R. Augusto Flávio da Silva</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>223390911 (dist=24.3m)</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>RUA AUGUSO FLAVIO DA SILVA 8, 8, SANTO ANTONIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>221807338</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>1442</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6064881,-46.9273043,3a,90y,79.8h,106.69t/data=!3m7!1e1!3m5!1sKwOlhG1tnUBbyXWvkZi5vA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-16.688546051672944%26panoid%3DKwOlhG1tnUBbyXWvkZi5vA%26yaw%3D79.80087525504709!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>RUA AUGUSTO FLAVIO DA SILVA 183, 183, ESTANCIA</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6064678921,-46.9272364796</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>COD ID_221807338 (linha 1442).jpg</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>excluir</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>4 R. José Carlos Pedro Grande</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>224292753 (dist=38.5m)</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>RUA JOSE CARLOS PEDRO GRANDE 215, 215, SANTO ANTONIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>221807338</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>1871</v>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6064881,-46.9273043,3a,90y,75.71h,124.68t/data=!3m7!1e1!3m5!1sKwOlhG1tnUBbyXWvkZi5vA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-34.68049983378164%26panoid%3DKwOlhG1tnUBbyXWvkZi5vA%26yaw%3D75.71413723888202!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>RUA AUGUSTO FLAVIO DA SILVA 183, 183, ESTANCIA</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6064678921,-46.9272364796</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>COD ID_221807338 (linha 1871).jpg</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>correto (confirmado por numero de poste) -&gt; movido pra ESQUINA - REVISAO</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>4 R. José Carlos Pedro Grande</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>224292753 (dist=38.5m)</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>RUA JOSE CARLOS PEDRO GRANDE 215, 215, SANTO ANTONIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>223455507</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6084602133,-46.9259161984</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>COD ID_223455507 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>223455507</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>1881</v>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6084705,-46.9255227,3a,75y,309.53h,110.16t/data=!3m7!1e1!3m5!1sLpM96QKRsnu3oYXeThn41w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-20.155084292637014%26panoid%3DLpM96QKRsnu3oYXeThn41w%26yaw%3D309.53178114004834!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>RUA IRINEIA ALVES DE PAIVA 90, 90, ESTANCIA</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6084602133,-46.9259161984</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>COD ID_223455507 (linha 1881).jpg</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>63 R. Irinéia Alves de Paiva</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>223977693</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6061297092,-46.9259170437</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>COD ID_223977693 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>223977693</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>1890</v>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6061005,-46.9259719,3a,75y,125.25h,124.23t/data=!3m7!1e1!3m5!1sZaDQQFbkK3sNayRjr7fwkg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-34.23307647789025%26panoid%3DZaDQQFbkK3sNayRjr7fwkg%26yaw%3D125.24893785515536!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>RUA OSVALDO ALVARO DA SILVA 29, 29, ESTANCIA</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6061297092,-46.9259170437</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>COD ID_223977693 (linha 1890).jpg</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>30 R. Osvaldo Álvaro da Silva</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>223255482</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>1848</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6092236,-46.9262704,3a,75y,286.75h,110.11t/data=!3m7!1e1!3m5!1s4qcJ2sGoLXO099ZMpjjHgQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-20.108916618629706%26panoid%3D4qcJ2sGoLXO099ZMpjjHgQ%26yaw%3D286.7524675659595!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>RUA NOEL FERREIRA BARBOSA 31, 31, ESTANCIA</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6091693332,-46.9263440868</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>COD ID_223255482 (linha 1848).jpg</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra POSTE UTILIZADO - REVISAO</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>78 R. Noel F Barbosa</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>223255482</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>1903</v>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6092236,-46.9262704,3a,75y,293.17h,106.32t/data=!3m7!1e1!3m5!1s4qcJ2sGoLXO099ZMpjjHgQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-16.32471067455475%26panoid%3D4qcJ2sGoLXO099ZMpjjHgQ%26yaw%3D293.1682030210564!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>RUA NOEL FERREIRA BARBOSA 31, 31, ESTANCIA</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6091693332,-46.9263440868</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>COD ID_223255482 (linha 1903).jpg</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>78 R. Noel F Barbosa</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>220853715</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>1847</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6091686,-46.925963,3a,75y,353.37h,117.68t/data=!3m7!1e1!3m5!1s-_ZcjSXZUOevzz5yowqB9Q!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-27.680986726069676%26panoid%3D-_ZcjSXZUOevzz5yowqB9Q%26yaw%3D353.3699150191866!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>RUA NOEL FERREIRA BARBOSA 20, 20, ESTANCIA</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6090825324,-46.9260093582</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>COD ID_220853715 (linha 1847).jpg</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra ESQUINA - REVISAO</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>146 R. Noel F Barbosa</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>220853715</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>1904</v>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6091686,-46.925963,3a,90y,351.7h,111.08t/data=!3m7!1e1!3m5!1s-_ZcjSXZUOevzz5yowqB9Q!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-21.080975058191868%26panoid%3D-_ZcjSXZUOevzz5yowqB9Q%26yaw%3D351.698733580459!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>RUA NOEL FERREIRA BARBOSA 20, 20, ESTANCIA</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6090825324,-46.9260093582</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>COD ID_220853715 (linha 1904).jpg</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>146 R. Noel F Barbosa</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>223977688</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>1846</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6090685,-46.9258966,3a,90y,249.61h,120.55t/data=!3m7!1e1!3m5!1sLmabsb82IepN6a9DUCYPJQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-30.554595859222673%26panoid%3DLmabsb82IepN6a9DUCYPJQ%26yaw%3D249.60753537910094!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>RUA ANTONIO PEREIRA DOS SANTOS 242, 242, ESTANCIA</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6090288132,-46.9259610781</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>COD ID_223977688 (linha 1846).jpg</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra ESQUINA - REVISAO</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>207 R. Antônio Pereira dos Santos</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>223977688</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>1905</v>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6090685,-46.9258966,3a,75y,248.06h,113.8t/data=!3m7!1e1!3m5!1sLmabsb82IepN6a9DUCYPJQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-23.79832338936572%26panoid%3DLmabsb82IepN6a9DUCYPJQ%26yaw%3D248.05792044566246!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>RUA ANTONIO PEREIRA DOS SANTOS 242, 242, ESTANCIA</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6090288132,-46.9259610781</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>COD ID_223977688 (linha 1905).jpg</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>207 R. Antônio Pereira dos Santos</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>224292683</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>1488</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.598462,-46.942098,3a,75y,112.17h,116.46t/data=!3m7!1e1!3m5!1sruZpoLXJzYeIkPvloshhSQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-26.46285407768019%26panoid%3DruZpoLXJzYeIkPvloshhSQ%26yaw%3D112.17227528012127!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AVENIDA DIVINO ALVES FERREIRA 493, 493, ESTANCIA</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6079896682,-46.9285318819</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>COD ID_224292683 (linha 1488).jpg</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>excluir</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>1635 Av. Pref. Aracely de Paula</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>219991722 (dist=8.4m)</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>AVENIDA PREFEITO ARACELY DE PAULA 1520, 1520, CENTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>224292683</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6080794,-46.9285446,3a,75y,14.36h,108.55t/data=!3m7!1e1!3m5!1svAOfNDzVcQLU6I_vOA7rEA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-18.552974767423677%26panoid%3DvAOfNDzVcQLU6I_vOA7rEA%26yaw%3D14.360348828196633!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AVENIDA DIVINO ALVES FERREIRA 493, 493, ESTANCIA</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6079896682,-46.9285318819</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>COD ID_224292683 (linha 2004).jpg</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>correto (confirmado por numero de poste) -&gt; movido pra POSTE UTILIZADO - REVISAO</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>821 Av. Divino Alves Ferreira</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>224318537</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2279</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.604686,-46.9208315,3a,75y,17.8h,101.71t/data=!3m7!1e1!3m5!1s_Kp0SgDC0pIcW0xIjxtNPg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-11.71288758838179%26panoid%3D_Kp0SgDC0pIcW0xIjxtNPg%26yaw%3D17.801712548075308!7i13312!8i6656?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>RUA TERENCIO PEREIRA 1690, 1690, SANTO ANTONIO</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6046125862,-46.9207993401</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>COD ID_224318537 (linha 2279).jpg</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra ESQUINA - REVISAO</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>2 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>219298647 (dist=45.0m)</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 35, 35, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>224318537</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>2291</v>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6046525,-46.9207691,3a,75y,303.79h,108.18t/data=!3m7!1e1!3m5!1sDkdbH2q5kO4aTkwlR7vSwA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-18.180000000000007%26panoid%3DDkdbH2q5kO4aTkwlR7vSwA%26yaw%3D303.79!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>RUA TERENCIO PEREIRA 1690, 1690, SANTO ANTONIO</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6046125862,-46.9207993401</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>COD ID_224318537 (linha 2291).jpg</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>25 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>219298647 (dist=37.6m)</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 35, 35, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>219298647</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2278</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6044767,-46.9205105,3a,75y,359.08h,100.09t/data=!3m7!1e1!3m5!1sdKG_gFuYLe-SiTQRK8vlUw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-10.086686662941403%26panoid%3DdKG_gFuYLe-SiTQRK8vlUw%26yaw%3D359.08270660094223!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 35, 35, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6044169027,-46.9205110876</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>COD ID_219298647 (linha 2278).jpg</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra POSTE UTILIZADO - REVISAO</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>35 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>219298647</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>2292</v>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6044767,-46.9205105,3a,75y,355.91h,104.64t/data=!3m7!1e1!3m5!1sdKG_gFuYLe-SiTQRK8vlUw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-14.643996089095694%26panoid%3DdKG_gFuYLe-SiTQRK8vlUw%26yaw%3D355.90902324153217!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 35, 35, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6044169027,-46.9205110876</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>COD ID_219298647 (linha 2292).jpg</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>35 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1038121887</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2277</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.604258,-46.9201952,3a,75y,271.28h,104.68t/data=!3m7!1e1!3m5!1sX_5pJK-0aBxSo0dAp2l8Sw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-14.679991447109643%26panoid%3DX_5pJK-0aBxSo0dAp2l8Sw%26yaw%3D271.2753135476118!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 65, 65, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6042393747,-46.9202230384</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>COD ID_1038121887 (linha 2277).jpg</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra POSTE UTILIZADO - REVISAO</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>65 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1038121887</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>2293</v>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6043121,-46.9202741,3a,75y,357.19h,105.94t/data=!3m7!1e1!3m5!1sVFl297rol1sqWEgaKU_TpQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-15.93709831685355%26panoid%3DVFl297rol1sqWEgaKU_TpQ%26yaw%3D357.19063875418334!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 65, 65, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6042393747,-46.9202230384</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>COD ID_1038121887 (linha 2293).jpg</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>60 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>220853786</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2276</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6040928,-46.9199601,3a,75y,346.4h,110.5t/data=!3m7!1e1!3m5!1sHDn__Vynz-Ck0gHDKVCY8w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-20.50250505099747%26panoid%3DHDn__Vynz-Ck0gHDKVCY8w%26yaw%3D346.4033770123561!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 85, 85, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6040435959,-46.9199442269</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>COD ID_220853786 (linha 2276).jpg</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra POSTE UTILIZADO - REVISAO</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>85 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>220853786</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>2294</v>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6040928,-46.9199601,3a,75y,346.15h,108.4t/data=!3m7!1e1!3m5!1sHDn__Vynz-Ck0gHDKVCY8w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-18.397368936623124%26panoid%3DHDn__Vynz-Ck0gHDKVCY8w%26yaw%3D346.1519333399381!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 85, 85, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6040435959,-46.9199442269</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>COD ID_220853786 (linha 2294).jpg</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>85 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>223390613</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2275</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6038845,-46.919647,3a,75y,327.1h,100.19t/data=!3m7!1e1!3m5!1spzqQZiJtIyXJQ8SnXuUXig!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-10.192577655297441%26panoid%3DpzqQZiJtIyXJQ8SnXuUXig%26yaw%3D327.0974985815046!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>RUA JULIA MARTA GUIMARAES 370, 370, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6038478162,-46.9196655118</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>COD ID_223390613 (linha 2275).jpg</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra POSTE UTILIZADO - REVISAO</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>124 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>220853786 (dist=35.8m)</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 85, 85, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>223390613</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>2295</v>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6038845,-46.919647,3a,75y,326.29h,102.08t/data=!3m7!1e1!3m5!1spzqQZiJtIyXJQ8SnXuUXig!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-12.08488407349293%26panoid%3DpzqQZiJtIyXJQ8SnXuUXig%26yaw%3D326.29310805888025!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>RUA JULIA MARTA GUIMARAES 370, 370, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6038478162,-46.9196655118</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>COD ID_223390613 (linha 2295).jpg</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>124 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>220853786 (dist=35.8m)</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 85, 85, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>219992126</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2274</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6036868,-46.9193631,3a,75y,348.95h,100.09t/data=!3m7!1e1!3m5!1sD-KviX9oS5-1Vky_mK5DZQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-10.092143404144068%26panoid%3DD-KviX9oS5-1Vky_mK5DZQ%26yaw%3D348.946909695841!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 135, 135, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6036522263,-46.9193677273</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>COD ID_219992126 (linha 2274).jpg</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra POSTE UTILIZADO - REVISAO</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>151 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>219992126</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>2296</v>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6036868,-46.9193631,3a,75y,342.03h,103.2t/data=!3m7!1e1!3m5!1sD-KviX9oS5-1Vky_mK5DZQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-13.195758168610752%26panoid%3DD-KviX9oS5-1Vky_mK5DZQ%26yaw%3D342.02909799900215!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 135, 135, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6036522263,-46.9193677273</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>COD ID_219992126 (linha 2296).jpg</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>151 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>222495333</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2273</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6034612,-46.9190481,3a,75y,293.85h,102.58t/data=!3m7!1e1!3m5!1syHMspG8IJXxQgPhPy6PeeQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-12.578660641775244%26panoid%3DyHMspG8IJXxQgPhPy6PeeQ%26yaw%3D293.8516925476748!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 175, 175, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6034654749,-46.919098554</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>COD ID_222495333 (linha 2273).jpg</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra POSTE UTILIZADO - REVISAO</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>175 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>222495333</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>2297</v>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6034612,-46.9190481,3a,75y,287.58h,103.8t/data=!3m7!1e1!3m5!1syHMspG8IJXxQgPhPy6PeeQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-13.804469092132251%26panoid%3DyHMspG8IJXxQgPhPy6PeeQ%26yaw%3D287.5849509606853!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 175, 175, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6034654749,-46.919098554</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>COD ID_222495333 (linha 2297).jpg</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>175 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>224357230</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2272</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6033011,-46.9188156,3a,75y,1.25h,103.73t/data=!3m7!1e1!3m5!1sDN6t1XOr8OyoZJTXigvzcA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-13.7318137272934%26panoid%3DDN6t1XOr8OyoZJTXigvzcA%26yaw%3D1.2495444377278204!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 200, 200, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6032696933,-46.9188198406</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>COD ID_224357230 (linha 2272).jpg</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra POSTE UTILIZADO - REVISAO</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>210 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>224357230</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>2298</v>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6033011,-46.9188156,3a,75y,355.02h,104.46t/data=!3m7!1e1!3m5!1sDN6t1XOr8OyoZJTXigvzcA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-14.456867448514373%26panoid%3DDN6t1XOr8OyoZJTXigvzcA%26yaw%3D355.0164903752741!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 200, 200, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6032696933,-46.9188198406</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>COD ID_224357230 (linha 2298).jpg</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>210 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>221703794</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2271</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6031023,-46.9185126,3a,75y,319.21h,105.53t/data=!3m7!1e1!3m5!1spnOwRYjazEWLl9JeViAiIA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-15.531630109540302%26panoid%3DpnOwRYjazEWLl9JeViAiIA%26yaw%3D319.2079588886102!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>RUA MARIA BENEDITA DE OLIVEIRA 395, 395, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6030649744,-46.9185314918</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>COD ID_221703794 (linha 2271).jpg</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra POSTE UTILIZADO - REVISAO</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>230 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>223977218 (dist=36.2m)</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 265, 265, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>221703794</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>2299</v>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6031023,-46.9185126,3a,75y,325.66h,108.79t/data=!3m7!1e1!3m5!1spnOwRYjazEWLl9JeViAiIA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-18.786210528419787%26panoid%3DpnOwRYjazEWLl9JeViAiIA%26yaw%3D325.6581040030028!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>RUA MARIA BENEDITA DE OLIVEIRA 395, 395, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6030649744,-46.9185314918</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>COD ID_221703794 (linha 2299).jpg</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>230 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>223977218 (dist=36.2m)</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 265, 265, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>223977218</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2270</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6028686,-46.9181906,3a,75y,268.24h,102.55t/data=!3m7!1e1!3m5!1soM9VI4o4BCQUHwE6WQ1yDw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-12.548813515100477%26panoid%3DoM9VI4o4BCQUHwE6WQ1yDw%26yaw%3D268.24043597813704!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 265, 265, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6028781312,-46.9182623194</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>COD ID_223977218 (linha 2270).jpg</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra POSTE UTILIZADO - REVISAO</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>270 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>223977218</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6029244,-46.9182695,3a,75y,5.09h,105.19t/data=!3m7!1e1!3m5!1saJNInnArpMMgondP3y7Vog!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-15.190184995144278%26panoid%3DaJNInnArpMMgondP3y7Vog%26yaw%3D5.08804600640919!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 265, 265, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6028781312,-46.9182623194</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>COD ID_223977218 (linha 2300).jpg</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>260 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>224357222</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2269</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6027041,-46.9179508,3a,75y,291.79h,99.43t/data=!3m7!1e1!3m5!1sKFbViAXiZCfnxWYzLECggQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-9.43037736719846%26panoid%3DKFbViAXiZCfnxWYzLECggQ%26yaw%3D291.787095673165!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 295, 295, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6026823434,-46.9179931433</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>COD ID_224357222 (linha 2269).jpg</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra POSTE UTILIZADO - REVISAO</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>295 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>224357222</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6027041,-46.9179508,3a,75y,290.27h,106.26t/data=!3m7!1e1!3m5!1sKFbViAXiZCfnxWYzLECggQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-16.25715370031081%26panoid%3DKFbViAXiZCfnxWYzLECggQ%26yaw%3D290.2737221673888!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 295, 295, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6026823434,-46.9179931433</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>COD ID_224357222 (linha 2301).jpg</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>295 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>219298660</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2268</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6025466,-46.9177174,3a,75y,350.55h,101.48t/data=!3m7!1e1!3m5!1s21liFUWXHkwjxT9vntayaA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-11.484352058101507%26panoid%3D21liFUWXHkwjxT9vntayaA%26yaw%3D350.54750156412587!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 325, 325, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6024866554,-46.9177048971</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>COD ID_219298660 (linha 2268).jpg</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra POSTE UTILIZADO - REVISAO</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>310 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>219298660</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>2302</v>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6025466,-46.9177174,3a,75y,346.01h,101.67t/data=!3m7!1e1!3m5!1s21liFUWXHkwjxT9vntayaA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-11.671736707144333%26panoid%3D21liFUWXHkwjxT9vntayaA%26yaw%3D346.0081255630487!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>RUA GILDO DUTRA 325, 325, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6024866554,-46.9177048971</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>COD ID_219298660 (linha 2302).jpg</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>310 R. Gildo Dutra</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>219298639</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2280</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/19%C2%B036'10.5%22S+46%C2%B055'07.3%22W/@-19.602936,-46.9187592,3a,75y,88.83h,95.28t/data=!3m7!1e1!3m5!1sM1lznJnTRLQit1vmZlV-ow!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-5.284037571363626%26panoid%3DM1lznJnTRLQit1vmZlV-ow%26yaw%3D88.83247370412491!7i16384!8i8192!4m4!3m3!8m2!3d-19.6029186!4d-46.9187013?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>RUA MARIA BENEDITA DE OLIVEIRA 390, 390, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.602918643,-46.9187013135</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>COD ID_219298639 (linha 2280).jpg</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra POSTE UTILIZADO - REVISAO</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>390 R. Maria Benedita de Oliveira</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>219298639</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>2304</v>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.602936,-46.9187592,3a,75y,88.11h,105.49t/data=!3m7!1e1!3m5!1sM1lznJnTRLQit1vmZlV-ow!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-15.494841599421122%26panoid%3DM1lznJnTRLQit1vmZlV-ow%26yaw%3D88.11285106656692!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>RUA MARIA BENEDITA DE OLIVEIRA 390, 390, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.602918643,-46.9187013135</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>COD ID_219298639 (linha 2304).jpg</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>390 R. Maria Benedita de Oliveira</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>223977216</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2281</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/19%C2%B036'10.5%22S+46%C2%B055'07.3%22W/@-19.602699,-46.918943,3a,75y,38.15h,96.91t/data=!3m7!1e1!3m5!1sAayX1B_1Yzc4F9TfgKoHsg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-6.914202363387844%26panoid%3DAayX1B_1Yzc4F9TfgKoHsg%26yaw%3D38.145307106305516!7i16384!8i8192!4m4!3m3!8m2!3d-19.6029186!4d-46.9187013?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>AVENIDA JOAQUIM BENEVIDES DE AVILA 292, 292, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6026545031,-46.9189078698</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>COD ID_223977216 (linha 2281).jpg</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra POSTE UTILIZADO - REVISAO</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>370 R. Maria Benedita de Oliveira</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>219298639 (dist=35.2m)</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>RUA MARIA BENEDITA DE OLIVEIRA 390, 390, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>223977216</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>2305</v>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.602699,-46.918943,3a,75y,40.35h,107.36t/data=!3m7!1e1!3m5!1sAayX1B_1Yzc4F9TfgKoHsg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-17.358820158508138%26panoid%3DAayX1B_1Yzc4F9TfgKoHsg%26yaw%3D40.35164551762587!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>AVENIDA JOAQUIM BENEVIDES DE AVILA 292, 292, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6026545031,-46.9189078698</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>COD ID_223977216 (linha 2305).jpg</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>370 R. Maria Benedita de Oliveira</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>219298639 (dist=35.2m)</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>RUA MARIA BENEDITA DE OLIVEIRA 390, 390, VEREDAS DA CIDADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>224357206</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6020401942,-46.9223034158</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>COD ID_224357206 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>224357206</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>2335</v>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/19%C2%B036'09.2%22S+46%C2%B055'19.1%22W/@-19.6020733,-46.9223126,3a,75y,253.87h,106.83t/data=!3m7!1e1!3m5!1s13s21DWo4MFFGqUTQEtcbg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-16.829345810917545%26panoid%3D13s21DWo4MFFGqUTQEtcbg%26yaw%3D253.8720051148694!7i16384!8i8192!4m4!3m3!8m2!3d-19.6025497!4d-46.9219664?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>RUA PADRE JOSE ZORZAL 30, 30, JOSE FERREIRA GUIMARAES</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6020401942,-46.9223034158</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>COD ID_224357206 (linha 2335).jpg</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>20 R. Padre José Zorzal</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>219992446</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>1920</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6086069,-46.9242362,3a,75y,271.29h,123.09t/data=!3m7!1e1!3m5!1s0AbAGq60unRG0hz_Dk0CjQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-33.08788178544678%26panoid%3D0AbAGq60unRG0hz_Dk0CjQ%26yaw%3D271.2940886979056!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>RUA EVITA GUIMARAES 120, 120, JOSE FERREIRA GUIMARAES</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6010987686,-46.9216441183</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>COD ID_219992446 (linha 1920).jpg</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra POSTE UTILIZADO - REVISAO</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>1319 R. Santo Antônio</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>219991194 (dist=5.9m)</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>RUA SANTO ANTONIO 1910, 1910, ESTANCIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>219992446</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>2357</v>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/19%C2%B036'06.0%22S+46%C2%B055'16.3%22W/@-19.601086,-46.9217054,3a,75y,96.64h,101.68t/data=!3m7!1e1!3m5!1suqTmCS3-5SNJ36XzedtXig!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-11.681578329987559%26panoid%3DuqTmCS3-5SNJ36XzedtXig%26yaw%3D96.63658786379214!7i16384!8i8192!4m4!3m3!8m2!3d-19.6016725!4d-46.9212029?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>RUA EVITA GUIMARAES 120, 120, JOSE FERREIRA GUIMARAES</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6010987686,-46.9216441183</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>COD ID_219992446 (linha 2357).jpg</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>61 R. Júlia Marta Guimarães</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>219992906</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6052620478,-46.9377549493</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>COD ID_219992906 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>219992906</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>2521</v>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.605211,-46.9377247,3a,90y,168.83h,107.7t/data=!3m7!1e1!3m5!1sAFvxwMZP36yMax1GAbjiIA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-17.704864584341593%26panoid%3DAFvxwMZP36yMax1GAbjiIA%26yaw%3D168.83210941983347!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyNC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>RUA PEDRO DIAS DE CARVALHO 381, 381, SANTA TEREZINHA</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6052620478,-46.9377549493</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>COD ID_219992906 (linha 2521).jpg</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>381 R. Pedro Dias de Carvalho</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>219992695</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6021851,-46.9318031,3a,43y,149.07h,115.41t/data=!3m7!1e1!3m5!1swIZPhy2-hnsFuLYFZIg0Ng!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-25.40643858956122%26panoid%3DwIZPhy2-hnsFuLYFZIg0Ng%26yaw%3D149.0734259729034!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyNC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>RUA CALIMERIO GUIMARAES 1581, 1581, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6022640696,-46.931771222</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>COD ID_219992695 (linha 1830).jpg</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>1567 R. Calimério Guimarães</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>219992695</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>2695</v>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6022794,-46.931794,3a,90y,41.47h,105.05t/data=!3m7!1e1!3m5!1svcvLkiVVSAy1uSvn5yPoJA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-15.04947030947352%26panoid%3DvcvLkiVVSAy1uSvn5yPoJA%26yaw%3D41.466849306929404!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>RUA CALIMERIO GUIMARAES 1581, 1581, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6022640696,-46.931771222</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>COD ID_219992695 (linha 2695).jpg</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>1598 R. Calimério Guimarães</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>220854438</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6025981,-46.9318103,3a,48.9y,88.78h,121.87t/data=!3m7!1e1!3m5!1sPIYYudQzZ0iLAjT0tC7OCg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-31.870011578498946%26panoid%3DPIYYudQzZ0iLAjT0tC7OCg%26yaw%3D88.78382324407308!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyNC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>RUA CALIMERIO GUIMARAES 1710, 1710, SAO VICENTE</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6025983836,-46.9317656246</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>COD ID_220854438 (linha 1831).jpg</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>1640 R. Calimério Guimarães</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>220854438</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>2696</v>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6025981,-46.9318103,3a,61.6y,86.08h,114.24t/data=!3m7!1e1!3m5!1sPIYYudQzZ0iLAjT0tC7OCg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-24.2367244424844%26panoid%3DPIYYudQzZ0iLAjT0tC7OCg%26yaw%3D86.08213719008143!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>RUA CALIMERIO GUIMARAES 1710, 1710, SAO VICENTE</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6025983836,-46.9317656246</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>COD ID_220854438 (linha 2696).jpg</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>1640 R. Calimério Guimarães</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>219385112</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>1832</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6029162,-46.9318197,3a,49y,155.03h,113.94t/data=!3m7!1e1!3m5!1sywSVkH7tkovceR7g8DbmuA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-23.941492124054093%26panoid%3DywSVkH7tkovceR7g8DbmuA%26yaw%3D155.0269053207359!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyNC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>RUA CALIMERIO GUIMARAES 1645, 1645, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6029682586,-46.9318081994</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>COD ID_219385112 (linha 1832).jpg</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>1667 R. Calimério Guimarães</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>219385112</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>2697</v>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6029162,-46.9318197,3a,46.9y,157.51h,107.32t/data=!3m7!1e1!3m5!1sywSVkH7tkovceR7g8DbmuA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-17.322612984026065%26panoid%3DywSVkH7tkovceR7g8DbmuA%26yaw%3D157.50621639416386!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>RUA CALIMERIO GUIMARAES 1645, 1645, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6029682586,-46.9318081994</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>COD ID_219385112 (linha 2697).jpg</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>1667 R. Calimério Guimarães</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>224357960</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>1833</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6033698,-46.9318731,3a,75y,96.54h,127.56t/data=!3m7!1e1!3m5!1sMa0JbTBF7vJxNKEMrIcl3A!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-37.55849503015507%26panoid%3DMa0JbTBF7vJxNKEMrIcl3A%26yaw%3D96.53547973940019!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyNC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>RUA MARIA RITA DE JESUS 2, 2, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6033469739,-46.9318699441</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>COD ID_224357960 (linha 1833).jpg</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>1715 R. Calimério Guimarães</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>224357413 (dist=43.2m)</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>RUA CALIMERIO GUIMARAES 1645, 1645, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>224357960</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>2698</v>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6034609,-46.9318836,3a,48.8y,25.97h,107.73t/data=!3m7!1e1!3m5!1sDVdc6XRCZt6QE99yscxZlA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-17.733922665998733%26panoid%3DDVdc6XRCZt6QE99yscxZlA%26yaw%3D25.973045101531337!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>RUA MARIA RITA DE JESUS 2, 2, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6033469739,-46.9318699441</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>COD ID_224357960 (linha 2698).jpg</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>1715 R. Calimério Guimarães</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>224357413 (dist=53.3m)</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>RUA CALIMERIO GUIMARAES 1645, 1645, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>219385071</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>1835</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6033302,-46.9317603,3a,46.9y,225.58h,117.79t/data=!3m7!1e1!3m5!1sM-57GGqVfYnI4F90BI2BhQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-27.7936053522682%26panoid%3DM-57GGqVfYnI4F90BI2BhQ%26yaw%3D225.5849220725482!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyNC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>RUA MARIA RITA DE JESUS 2, 2, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6033204448,-46.9318219689</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>COD ID_219385071 (linha 1835).jpg</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>2 R. Maria Rita de Jesus</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>219385071</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>2699</v>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6033302,-46.9317603,3a,48.9y,226.41h,113.02t/data=!3m7!1e1!3m5!1sM-57GGqVfYnI4F90BI2BhQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-23.015072234345013%26panoid%3DM-57GGqVfYnI4F90BI2BhQ%26yaw%3D226.41270420334098!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>RUA MARIA RITA DE JESUS 2, 2, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6033204448,-46.9318219689</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>COD ID_219385071 (linha 2699).jpg</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>2 R. Maria Rita de Jesus</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>223455683</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>1834</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6037451,-46.9319173,3a,48.9y,36.1h,117.04t/data=!3m7!1e1!3m5!1shCC9MYxDbFXWURdwDw52Eg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-27.042327310182486%26panoid%3DhCC9MYxDbFXWURdwDw52Eg%26yaw%3D36.09682308395033!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyNC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>AVENIDA JOAO MOREIRA SALLES 45, 45, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.603662742,-46.9319118175</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>COD ID_223455683 (linha 1834).jpg</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>1783 R. Calimério Guimarães</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>223455683</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6037451,-46.9319173,3a,75.5y,36.08h,106.92t/data=!3m7!1e1!3m5!1shCC9MYxDbFXWURdwDw52Eg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-16.915179338550885%26panoid%3DhCC9MYxDbFXWURdwDw52Eg%26yaw%3D36.080230333216264!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>AVENIDA JOAO MOREIRA SALLES 45, 45, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.603662742,-46.9319118175</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>COD ID_223455683 (linha 2700).jpg</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>1783 R. Calimério Guimarães</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>224357413</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>1836</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6030574,-46.9317231,3a,48.9y,317.01h,119.38t/data=!3m7!1e1!3m5!1sF_P05hnyDg9QK0IWZn8yUw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-29.38174466123135%26panoid%3DF_P05hnyDg9QK0IWZn8yUw%26yaw%3D317.0149720539556!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyNC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>RUA CALIMERIO GUIMARAES 1645, 1645, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6029958354,-46.9317609256</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>COD ID_224357413 (linha 1836).jpg</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>1 Tv. Santa Ediges</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>223977524 (dist=39.2m)</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>TRAVESSA SANTA EDWIGES 101, 101, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>224357413</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>2740</v>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6030574,-46.9317231,3a,67.8y,314.19h,107.09t/data=!3m7!1e1!3m5!1sF_P05hnyDg9QK0IWZn8yUw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-17.093134185663445%26panoid%3DF_P05hnyDg9QK0IWZn8yUw%26yaw%3D314.1932351339775!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>RUA CALIMERIO GUIMARAES 1645, 1645, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6029958354,-46.9317609256</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>COD ID_224357413 (linha 2740).jpg</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>1 Tv. Santa Ediges</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>223977524 (dist=39.2m)</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>TRAVESSA SANTA EDWIGES 101, 101, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>219992636</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>1837</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6027312,-46.9314666,3a,72.1y,155.26h,114.22t/data=!3m7!1e1!3m5!1s-wQlQ5WOanes9Dihd0L1fg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-24.222005353718004%26panoid%3D-wQlQ5WOanes9Dihd0L1fg%26yaw%3D155.26445525441451!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyNC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>RUA CALIMERIO GUIMARAES 1635, 1635, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6027254182,-46.9317100258</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>COD ID_219992636 (linha 1837).jpg</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>30 R. Lázaro Ferreira dos Santos</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>220854341 (dist=4.7m)</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>RUA LAZARO FERREIRA DOS SANTOS 40, 40, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>219992636</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>2746</v>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6026875,-46.9316796,3a,63.6y,237.11h,109.57t/data=!3m7!1e1!3m5!1s9Ysukz9kQibluctvX8dNuw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-19.565473848755488%26panoid%3D9Ysukz9kQibluctvX8dNuw%26yaw%3D237.1081426784255!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>RUA CALIMERIO GUIMARAES 1635, 1635, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6027254182,-46.9317100258</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>COD ID_219992636 (linha 2746).jpg</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>1 R. Lázaro Ferreira dos Santos</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>220854341 (dist=24.6m)</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>RUA LAZARO FERREIRA DOS SANTOS 40, 40, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>221807340</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>1869</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6059486,-46.9274505,3a,75y,20.72h,112.37t/data=!3m7!1e1!3m5!1sCQT7eLAKCeVdu_HANFhNGQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-22.370601664342843%26panoid%3DCQT7eLAKCeVdu_HANFhNGQ%26yaw%3D20.71751988629301!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>RUA JOSE CARLOS PEDRO GRANDE 205, 205, SANTO ANTONIO</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6059157371,-46.9273442579</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>COD ID_221807340 (linha 1869).jpg</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra POSTE UTILIZADO - REVISAO</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>205 R. José Carlos Pedro Grande</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>221807340</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>2799</v>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6059486,-46.9274505,3a,51.1y,20.13h,98.3t/data=!3m7!1e1!3m5!1sCQT7eLAKCeVdu_HANFhNGQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-8.295866632015873%26panoid%3DCQT7eLAKCeVdu_HANFhNGQ%26yaw%3D20.134905079379415!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>RUA JOSE CARLOS PEDRO GRANDE 205, 205, SANTO ANTONIO</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6059157371,-46.9273442579</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>COD ID_221807340 (linha 2799).jpg</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>205 R. José Carlos Pedro Grande</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>224292753</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>1870</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6061397,-46.9273875,3a,90y,110.48h,119.66t/data=!3m7!1e1!3m5!1sd3fCWUpnm7pJ2yAYQkIY2g!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-29.657797848660834%26panoid%3Dd3fCWUpnm7pJ2yAYQkIY2g%26yaw%3D110.47840770453301!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>RUA JOSE CARLOS PEDRO GRANDE 215, 215, SANTO ANTONIO</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.606142038,-46.9272992999</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>COD ID_224292753 (linha 1870).jpg</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra POSTE UTILIZADO - REVISAO</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>245 R. José Carlos Pedro Grande</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>224292753</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>2800</v>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6061397,-46.9273875,3a,75y,102.79h,103.11t/data=!3m7!1e1!3m5!1sd3fCWUpnm7pJ2yAYQkIY2g!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-13.106915651963703%26panoid%3Dd3fCWUpnm7pJ2yAYQkIY2g%26yaw%3D102.7870409511928!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>RUA JOSE CARLOS PEDRO GRANDE 215, 215, SANTO ANTONIO</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.606142038,-46.9272992999</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>COD ID_224292753 (linha 2800).jpg</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>245 R. José Carlos Pedro Grande</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>219992413</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6016431183,-46.9239572187</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>COD ID_219992413 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>excluir</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>219992413</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>2988</v>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/19%C2%B036'05.9%22S+46%C2%B055'26.3%22W/@-19.6016378,-46.9240031,3a,75y,128.23h,90t/data=!3m7!1e1!3m5!1sh4R1vzYestTWH6uV2UUefA!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D0%26panoid%3Dh4R1vzYestTWH6uV2UUefA%26yaw%3D128.22986!7i16384!8i8192!4m4!3m3!8m2!3d-19.6016431!4d-46.9239572?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>RUA LAZARO PAULISTA 30, 30, SANTO ANTONIO</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6016431183,-46.9239572187</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>COD ID_219992413 (linha 2988).jpg</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>correto (confirmado por numero de poste) -&gt; movido pra POSTE UTILIZADO - REVISAO</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>51 R. Lázaro Paulista</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>221703720</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>2666</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>460 R. Guarani - Google Maps</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>RUA GUARANI 450, 450, SANTO ANTONIO</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6021573813,-46.926556066</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>COD ID_221703720 (linha 2666).jpg</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra POSTE UTILIZADO - REVISAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>221703720</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/19%C2%B036'07.8%22S+46%C2%B055'35.6%22W/@-19.6021833,-46.9265436,3a,75y,330.17h,90t/data=!3m7!1e1!3m5!1sYG4wE_kmNSJvP3NhHtqESQ!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D0%26panoid%3DYG4wE_kmNSJvP3NhHtqESQ%26yaw%3D330.16827!7i16384!8i8192!4m4!3m3!8m2!3d-19.6021574!4d-46.9265561?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>RUA GUARANI 450, 450, SANTO ANTONIO</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6021573813,-46.926556066</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>COD ID_221703720 (linha 3006).jpg</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>450 R. Guarani</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>222495512</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6021892451,-46.9261084402</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>COD ID_222495512 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>222495512</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>3009</v>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/19%C2%B036'07.9%22S+46%C2%B055'34.0%22W/@-19.6021324,-46.9260798,3a,75y,183.84h,104.5t/data=!3m7!1e1!3m5!1sNJ0TIT7GNPe-prxAgaZp2w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-14.501550621820726%26panoid%3DNJ0TIT7GNPe-prxAgaZp2w%26yaw%3D183.8353231068666!7i16384!8i8192!4m4!3m3!8m2!3d-19.6021892!4d-46.9261084?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>AVENIDA CASSIANO DE PAULA NASCIMENTO 120, 120, SANTO ANTONIO</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6021892451,-46.9261084402</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>COD ID_222495512 (linha 3009).jpg</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>(sem dado de rua)</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>224496375</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6099883269,-46.9358861105</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>COD ID_224496375 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>224496375</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>3146</v>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6099437,-46.9359743,3a,63.7y,81.54h,109.71t/data=!3m7!1e1!3m5!1s3pyqnheIC_ouz9UZUfrsgg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-19.710997148486285%26panoid%3D3pyqnheIC_ouz9UZUfrsgg%26yaw%3D81.53905201437317!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>RUA MARISA ANGELA MARCONDES 100, 100, LEDA BARCELOS</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6099883269,-46.9358861105</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>COD ID_224496375 (linha 3146).jpg</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>122 R. Dulce Mascarenhas Torres</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>224494788 (dist=84.5m)</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>RUA DULCE MASCARENHAS TORRES 80, 80, LEDA BARCELOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>219090673</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.610573898,-46.9351972253</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>COD ID_219090673 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>219090673</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>3149</v>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6105718,-46.9351329,3a,90y,303.66h,110.48t/data=!3m7!1e1!3m5!1sVf_umGT2wpPUQDJi0lAn1Q!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-20.481344347933998%26panoid%3DVf_umGT2wpPUQDJi0lAn1Q%26yaw%3D303.6644874871778!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>AVENIDA PEDRO HONORATO DA SILVA 380, 380, LEDA BARCELOS</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.610573898,-46.9351972253</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>COD ID_219090673 (linha 3149).jpg</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>1420 Av. Pedro Honorato da Silva</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>221094758</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>lote anterior</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6106212662,-46.9349880592</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>COD ID_221094758 (linha lote anterior).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>221094758</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>3162</v>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.610531,-46.9349858,3a,46.9y,152.98h,105.34t/data=!3m7!1e1!3m5!1shQtczeG9HSFQO0JXFMYm-A!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-15.344857592434863%26panoid%3DhQtczeG9HSFQO0JXFMYm-A%26yaw%3D152.9751142578928!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>AVENIDA PEDRO HONORATO DA SILVA 380, 380, LEDA BARCELOS</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6106212662,-46.9349880592</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>COD ID_221094758 (linha 3162).jpg</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>1395 Av. Pedro Honorato da Silva</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>224102940</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>1858</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6081473,-46.9275723,3a,90y,263.98h,116.47t/data=!3m7!1e1!3m5!1s7Zqq3YxfBa9r6h_WDuWb_w!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-26.46815865867144%26panoid%3D7Zqq3YxfBa9r6h_WDuWb_w%26yaw%3D263.98191400552093!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>AVENIDA DAMASO DRUMMOND 455, 455, JOSE FERREIRA GUIMARAES</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5931727574,-46.928774752</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>COD ID_224102940 (linha 1858).jpg</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>mesmo Poste nos dois lados -- mantido este, movido pra POSTE UTILIZADO - REVISAO</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>145 R. Ferreira Benfica</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>223390910 (dist=5.4m)</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>RUA FERREIRA BENFICA 180, 180, ESTANCIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>224102940</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.5931969,-46.9286933,960a,75y,230.29h,123.11t/data=!3m7!1e1!3m5!1sNA9a2uVGq8DpAjun34ufHg!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D-33.11378666318966%26panoid%3DNA9a2uVGq8DpAjun34ufHg%26yaw%3D230.28648447815766!7i16384!8i8192?entry=ttu&amp;g_ep=EgoyMDI2MDgyMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>AVENIDA DAMASO DRUMMOND 455, 455, JOSE FERREIRA GUIMARAES</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.5931727574,-46.928774752</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>COD ID_224102940 (linha 2019).jpg</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>excluir (duplicata do mesmo Poste, outro lado mantido)</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>311 Av. Dâmaso Drumond</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>1358664540</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>2694</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>1550 R. Calimério Guimarães - Google Maps</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>RUA CALIMERIO GUIMARAES 1509, 1509, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6019656971,-46.9317961979</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>COD ID_1358664540 (linha 2694).jpg</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>1358664540</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>1829</v>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@-19.6019994,-46.9318052,3a,80y,16.62h,82t/data=!3m6!1e1!3m4!1sO9MMx04IbShkxBsS0XZOZQ!2e0!7i16384!8i8192</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>RUA CALIMERIO GUIMARAES 1509, 1509, DOUTOR PEDRO PEZZUTI</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=-19.6019656971,-46.9317961979</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>COD ID_1358664540 (linha 1829).jpg</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>1550 R. Calimério Guimarães</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -7513,6 +11401,172 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId286"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId287"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F166" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F190" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F191" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F192" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F193" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F194" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F195" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F196" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F197" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F198" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F203" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F204" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F205" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F206" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F207" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F208" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F209" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F210" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F211" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F212" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F213" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F214" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F215" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F216" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F217" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F218" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F219" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F220" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F221" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F222" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F223" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F224" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F225" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F226" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D227" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F227" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D228" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F228" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D229" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F229" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D230" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F230" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D231" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F231" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D232" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F232" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D233" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F233" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D234" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F234" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F235" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D236" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F236" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F237" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F238" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F239" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F240" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F241" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F242" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F243" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F244" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F245" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D246" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F246" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D247" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F247" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F248" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F249" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F250" r:id="rId454"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
